--- a/HolidayCalendarService/Template/Power Platform Deutsch.xlsx
+++ b/HolidayCalendarService/Template/Power Platform Deutsch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicoschreder\Development\adventcalendarapp\HolidayCalendarService\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303AD5A9-1115-49B6-A640-2C1BDE5DAF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB2895E-1BFC-4CBA-90B3-A39F3F8119E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18150" yWindow="-70" windowWidth="16960" windowHeight="15370" xr2:uid="{DA429942-75DC-4399-AA24-F29984099B9A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{DA429942-75DC-4399-AA24-F29984099B9A}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
   <si>
     <t>publishDate</t>
   </si>
@@ -199,13 +199,19 @@
   </si>
   <si>
     <t>https://customers.microsoft.com/de-de/search?sq=&amp;ff=language%26%3EDeutsch%26%26story_product_categories%26%3EPower%20Apps&amp;p=0&amp;so=story_publish_date%20desc</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Power%20Platform%20Deutsch/15.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Power%20Platform%20Deutsch/24.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,14 +221,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -245,17 +243,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -621,7 +616,7 @@
       <c r="B2" s="1">
         <v>44896</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>32</v>
       </c>
       <c r="D2" t="s">
@@ -635,7 +630,7 @@
       <c r="B3" s="1">
         <v>44897</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>33</v>
       </c>
       <c r="D3" t="s">
@@ -649,7 +644,7 @@
       <c r="B4" s="1">
         <v>44898</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>34</v>
       </c>
       <c r="D4" t="s">
@@ -663,7 +658,7 @@
       <c r="B5" s="1">
         <v>44899</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>35</v>
       </c>
       <c r="D5" t="s">
@@ -677,7 +672,7 @@
       <c r="B6" s="1">
         <v>44900</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>36</v>
       </c>
       <c r="D6" t="s">
@@ -691,7 +686,7 @@
       <c r="B7" s="1">
         <v>44901</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>37</v>
       </c>
       <c r="D7" t="s">
@@ -705,7 +700,7 @@
       <c r="B8" s="1">
         <v>44902</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>38</v>
       </c>
       <c r="D8" t="s">
@@ -719,7 +714,7 @@
       <c r="B9" s="1">
         <v>44903</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>39</v>
       </c>
       <c r="D9" t="s">
@@ -733,7 +728,7 @@
       <c r="B10" s="1">
         <v>44904</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>40</v>
       </c>
       <c r="D10" t="s">
@@ -747,7 +742,7 @@
       <c r="B11" s="1">
         <v>44905</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>41</v>
       </c>
       <c r="D11" t="s">
@@ -761,7 +756,7 @@
       <c r="B12" s="1">
         <v>44906</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s">
         <v>42</v>
       </c>
       <c r="D12" t="s">
@@ -775,7 +770,7 @@
       <c r="B13" s="1">
         <v>44907</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s">
         <v>43</v>
       </c>
       <c r="D13" t="s">
@@ -789,7 +784,7 @@
       <c r="B14" s="1">
         <v>44908</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s">
         <v>44</v>
       </c>
       <c r="D14" t="s">
@@ -803,7 +798,7 @@
       <c r="B15" s="1">
         <v>44909</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s">
         <v>45</v>
       </c>
       <c r="D15" t="s">
@@ -817,6 +812,9 @@
       <c r="B16" s="1">
         <v>44910</v>
       </c>
+      <c r="C16" t="s">
+        <v>54</v>
+      </c>
       <c r="D16" t="s">
         <v>4</v>
       </c>
@@ -828,7 +826,7 @@
       <c r="B17" s="1">
         <v>44911</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s">
         <v>46</v>
       </c>
       <c r="D17" t="s">
@@ -842,7 +840,7 @@
       <c r="B18" s="1">
         <v>44912</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s">
         <v>47</v>
       </c>
       <c r="D18" t="s">
@@ -856,7 +854,7 @@
       <c r="B19" s="1">
         <v>44913</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s">
         <v>48</v>
       </c>
       <c r="D19" t="s">
@@ -870,7 +868,7 @@
       <c r="B20" s="1">
         <v>44914</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>49</v>
       </c>
       <c r="D20" t="s">
@@ -884,7 +882,7 @@
       <c r="B21" s="1">
         <v>44915</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s">
         <v>50</v>
       </c>
       <c r="D21" t="s">
@@ -898,7 +896,7 @@
       <c r="B22" s="1">
         <v>44916</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s">
         <v>51</v>
       </c>
       <c r="D22" t="s">
@@ -912,7 +910,7 @@
       <c r="B23" s="1">
         <v>44917</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" t="s">
         <v>52</v>
       </c>
       <c r="D23" t="s">
@@ -926,7 +924,7 @@
       <c r="B24" s="1">
         <v>44918</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" t="s">
         <v>53</v>
       </c>
       <c r="D24" t="s">
@@ -940,41 +938,19 @@
       <c r="B25" s="1">
         <v>44919</v>
       </c>
-      <c r="C25" s="2"/>
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
       <c r="D25" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="C7" r:id="rId1" xr:uid="{9D70A3C8-8198-4E02-9DAC-ECA0CA3B941C}"/>
-    <hyperlink ref="C12" r:id="rId2" xr:uid="{1CE47DA8-ED61-4493-AA88-F050728C301F}"/>
-    <hyperlink ref="C17" r:id="rId3" xr:uid="{0EFE390A-E071-43D4-97A2-C6ACA3BB4D7A}"/>
-    <hyperlink ref="C22" r:id="rId4" xr:uid="{F31A7134-258F-474B-AF28-509F7BE9A040}"/>
-    <hyperlink ref="C2" r:id="rId5" xr:uid="{11D1FE43-71AB-439B-9810-7AEB56596A14}"/>
-    <hyperlink ref="C3" r:id="rId6" xr:uid="{63A27322-FD80-4EF8-A5F5-D0B19657FFFA}"/>
-    <hyperlink ref="C4" r:id="rId7" xr:uid="{E049AE05-1DA1-4A2A-8538-D175E2BCC667}"/>
-    <hyperlink ref="C5" r:id="rId8" xr:uid="{3DA3BF52-D7EF-4ACC-B94B-B5905485DFD0}"/>
-    <hyperlink ref="C6" r:id="rId9" xr:uid="{172023E2-A1DB-42BC-AD6F-6B6BBBCFEC9E}"/>
-    <hyperlink ref="C8" r:id="rId10" location=":~:text=Maker%20matching%20with%20an%20integrated%20virtual%20agent%20in,well%20as%20internal%20resources%20specific%20to%20an%20organization" display="https://powerapps.microsoft.com/de-de/blog/power-apps-brings-collaboration-to-center-stage-with-3-big-announcements/#:~:text=Maker%20matching%20with%20an%20integrated%20virtual%20agent%20in,well%20as%20internal%20resources%20specific%20to%20an%20organization" xr:uid="{D3E05260-B1C3-453E-85A1-A036D9BF0D9B}"/>
-    <hyperlink ref="C9" r:id="rId11" xr:uid="{C1D8D7DB-CBA5-4587-8F63-6A1A32E966C7}"/>
-    <hyperlink ref="C10" r:id="rId12" location="design-your-app-in-figma" xr:uid="{17AA18A1-0AC6-4D2B-92E9-5A1698D8A3C8}"/>
-    <hyperlink ref="C11" r:id="rId13" xr:uid="{629561AA-C605-44D0-92DC-906BD99B4C02}"/>
-    <hyperlink ref="C13" r:id="rId14" xr:uid="{CEC8D436-4BE0-43CD-821A-6B998EFA735A}"/>
-    <hyperlink ref="C14" r:id="rId15" xr:uid="{82C41DAF-C49B-4064-AC9A-C5C9471E58BE}"/>
-    <hyperlink ref="C15" r:id="rId16" xr:uid="{68AE2349-4430-4DB7-A863-99805DE47577}"/>
-    <hyperlink ref="C18" r:id="rId17" xr:uid="{D82133B4-09A4-4C5D-8D76-F6ED847F642C}"/>
-    <hyperlink ref="C19" r:id="rId18" xr:uid="{A3901757-4C11-46EA-B756-E68797DDA3D1}"/>
-    <hyperlink ref="C20" r:id="rId19" xr:uid="{596D67BA-59E5-46B6-A214-D3432BDC6890}"/>
-    <hyperlink ref="C21" r:id="rId20" xr:uid="{A6D86229-6F05-4F52-ACB6-DC873679AE20}"/>
-    <hyperlink ref="C23" r:id="rId21" xr:uid="{EBA7CB4A-078C-46F2-A498-2BE3AE8CFCF9}"/>
-    <hyperlink ref="C24" r:id="rId22" xr:uid="{AE4E798B-F699-4548-83CE-41572EE8372F}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId23"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId24"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
